--- a/artfynd/A 2349-2025 artfynd.xlsx
+++ b/artfynd/A 2349-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,347 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123271389</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>582977</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7041098</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123271148</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>583019</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7041166</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123271332</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>583006</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7041124</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2349-2025 artfynd.xlsx
+++ b/artfynd/A 2349-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123271389</v>
+        <v>123271332</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582977</v>
+        <v>583006</v>
       </c>
       <c r="R3" t="n">
-        <v>7041098</v>
+        <v>7041124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123271332</v>
+        <v>123271389</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583006</v>
+        <v>582977</v>
       </c>
       <c r="R5" t="n">
-        <v>7041124</v>
+        <v>7041098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2349-2025 artfynd.xlsx
+++ b/artfynd/A 2349-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123271332</v>
+        <v>123271148</v>
       </c>
       <c r="B3" t="n">
-        <v>90952</v>
+        <v>56688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +804,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583006</v>
+        <v>583019</v>
       </c>
       <c r="R3" t="n">
-        <v>7041124</v>
+        <v>7041166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123271148</v>
+        <v>123271389</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,43 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583019</v>
+        <v>582977</v>
       </c>
       <c r="R4" t="n">
-        <v>7041166</v>
+        <v>7041098</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123271389</v>
+        <v>123271332</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582977</v>
+        <v>583006</v>
       </c>
       <c r="R5" t="n">
-        <v>7041098</v>
+        <v>7041124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2349-2025 artfynd.xlsx
+++ b/artfynd/A 2349-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122846021</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123271148</v>
+        <v>123271332</v>
       </c>
       <c r="B3" t="n">
-        <v>56688</v>
+        <v>90955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583019</v>
+        <v>583006</v>
       </c>
       <c r="R3" t="n">
-        <v>7041166</v>
+        <v>7041124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123271389</v>
+        <v>123271148</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,38 +916,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582977</v>
+        <v>583019</v>
       </c>
       <c r="R4" t="n">
-        <v>7041098</v>
+        <v>7041166</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123271332</v>
+        <v>123271389</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>78769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583006</v>
+        <v>582977</v>
       </c>
       <c r="R5" t="n">
-        <v>7041124</v>
+        <v>7041098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2349-2025 artfynd.xlsx
+++ b/artfynd/A 2349-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123271332</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123271148</v>
+        <v>123271389</v>
       </c>
       <c r="B4" t="n">
-        <v>56691</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,43 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583019</v>
+        <v>582977</v>
       </c>
       <c r="R4" t="n">
-        <v>7041166</v>
+        <v>7041098</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123271389</v>
+        <v>123271148</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>56691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,38 +1028,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582977</v>
+        <v>583019</v>
       </c>
       <c r="R5" t="n">
-        <v>7041098</v>
+        <v>7041166</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2349-2025 artfynd.xlsx
+++ b/artfynd/A 2349-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123271332</v>
+        <v>123271148</v>
       </c>
       <c r="B3" t="n">
-        <v>90957</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +804,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583006</v>
+        <v>583019</v>
       </c>
       <c r="R3" t="n">
-        <v>7041124</v>
+        <v>7041166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +912,7 @@
         <v>123271389</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123271148</v>
+        <v>123271332</v>
       </c>
       <c r="B5" t="n">
-        <v>56691</v>
+        <v>90963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,43 +1033,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583019</v>
+        <v>583006</v>
       </c>
       <c r="R5" t="n">
-        <v>7041166</v>
+        <v>7041124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2349-2025 artfynd.xlsx
+++ b/artfynd/A 2349-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123271148</v>
+        <v>123271332</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583019</v>
+        <v>583006</v>
       </c>
       <c r="R3" t="n">
-        <v>7041166</v>
+        <v>7041124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123271332</v>
+        <v>123271389</v>
       </c>
       <c r="B4" t="n">
-        <v>90966</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583006</v>
+        <v>582977</v>
       </c>
       <c r="R4" t="n">
-        <v>7041124</v>
+        <v>7041098</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123271389</v>
+        <v>123271148</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>56697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,38 +1028,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582977</v>
+        <v>583019</v>
       </c>
       <c r="R5" t="n">
-        <v>7041098</v>
+        <v>7041166</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2349-2025 artfynd.xlsx
+++ b/artfynd/A 2349-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123271332</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123271389</v>
+        <v>123271148</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +916,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582977</v>
+        <v>583019</v>
       </c>
       <c r="R4" t="n">
-        <v>7041098</v>
+        <v>7041166</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123271148</v>
+        <v>123271389</v>
       </c>
       <c r="B5" t="n">
-        <v>56697</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,43 +1033,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583019</v>
+        <v>582977</v>
       </c>
       <c r="R5" t="n">
-        <v>7041166</v>
+        <v>7041098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2349-2025 artfynd.xlsx
+++ b/artfynd/A 2349-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123271332</v>
       </c>
       <c r="B3" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123271148</v>
+        <v>123271389</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,43 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583019</v>
+        <v>582977</v>
       </c>
       <c r="R4" t="n">
-        <v>7041166</v>
+        <v>7041098</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123271389</v>
+        <v>123271148</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,38 +1028,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582977</v>
+        <v>583019</v>
       </c>
       <c r="R5" t="n">
-        <v>7041098</v>
+        <v>7041166</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2349-2025 artfynd.xlsx
+++ b/artfynd/A 2349-2025 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123271389</v>
+        <v>123271148</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +916,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582977</v>
+        <v>583019</v>
       </c>
       <c r="R4" t="n">
-        <v>7041098</v>
+        <v>7041166</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123271148</v>
+        <v>123271389</v>
       </c>
       <c r="B5" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,43 +1033,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583019</v>
+        <v>582977</v>
       </c>
       <c r="R5" t="n">
-        <v>7041166</v>
+        <v>7041098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2349-2025 artfynd.xlsx
+++ b/artfynd/A 2349-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123271332</v>
+        <v>123271148</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +804,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583006</v>
+        <v>583019</v>
       </c>
       <c r="R3" t="n">
-        <v>7041124</v>
+        <v>7041166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123271148</v>
+        <v>123271389</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,43 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583019</v>
+        <v>582977</v>
       </c>
       <c r="R4" t="n">
-        <v>7041166</v>
+        <v>7041098</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123271389</v>
+        <v>123271332</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582977</v>
+        <v>583006</v>
       </c>
       <c r="R5" t="n">
-        <v>7041098</v>
+        <v>7041124</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2349-2025 artfynd.xlsx
+++ b/artfynd/A 2349-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123271148</v>
+        <v>123271389</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583019</v>
+        <v>582977</v>
       </c>
       <c r="R3" t="n">
-        <v>7041166</v>
+        <v>7041098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123271389</v>
+        <v>123271332</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582977</v>
+        <v>583006</v>
       </c>
       <c r="R4" t="n">
-        <v>7041098</v>
+        <v>7041124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123271332</v>
+        <v>123271148</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,38 +1028,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583006</v>
+        <v>583019</v>
       </c>
       <c r="R5" t="n">
-        <v>7041124</v>
+        <v>7041166</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
